--- a/agriculture 41.xlsx
+++ b/agriculture 41.xlsx
@@ -223,6 +223,9 @@
     <t xml:space="preserve">2019-20</t>
   </si>
   <si>
+    <t xml:space="preserve">Unit:- nut/hector</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b val="true"/>
@@ -246,10 +249,27 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Source Description:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1965-66 to 2007-08: Plantation Crops: Coconut:-&gt; Directorate of Economics and Statistics, Dept. of Agriculture, Cooperation and Farmers Welfare, Ministry of Agriculture, Govt. of India</t>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Source Description: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1965-66 to 2007-08: Plantation Crops: Coconut:-&gt; Directorate of Economics and Statistics, Dept. of Agriculture, Cooperation and Farmers Welfare, Ministry of Agriculture, Govt. of India</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">2008-09 to 2016-17: Plantation Crops: Coconut:-&gt; Indian Horticulture Database, National Horticulture Board</t>
@@ -2504,49 +2524,99 @@
         <v>-0.272719980749178</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="30.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="9" t="s">
+    <row r="56" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B56" s="9"/>
-      <c r="C56" s="9"/>
-    </row>
-    <row r="57" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="10" t="s">
+      <c r="B56" s="3"/>
+      <c r="C56" s="3"/>
+      <c r="D56" s="3"/>
+      <c r="E56" s="3"/>
+      <c r="F56" s="3"/>
+      <c r="G56" s="3"/>
+      <c r="H56" s="3"/>
+      <c r="I56" s="3"/>
+      <c r="J56" s="3"/>
+      <c r="K56" s="3"/>
+      <c r="L56" s="3"/>
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" customFormat="false" ht="30.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="B57" s="10"/>
-      <c r="C57" s="10"/>
-    </row>
-    <row r="58" customFormat="false" ht="110.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="11" t="s">
+      <c r="B57" s="9"/>
+      <c r="C57" s="9"/>
+      <c r="D57" s="9"/>
+      <c r="E57" s="9"/>
+      <c r="F57" s="9"/>
+      <c r="G57" s="9"/>
+      <c r="H57" s="9"/>
+      <c r="I57" s="9"/>
+      <c r="J57" s="9"/>
+      <c r="K57" s="9"/>
+      <c r="L57" s="9"/>
+      <c r="M57" s="9"/>
+    </row>
+    <row r="58" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="B58" s="11"/>
-      <c r="C58" s="11"/>
-    </row>
-    <row r="59" customFormat="false" ht="61.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B58" s="10"/>
+      <c r="C58" s="10"/>
+      <c r="D58" s="10"/>
+      <c r="E58" s="10"/>
+      <c r="F58" s="10"/>
+      <c r="G58" s="10"/>
+      <c r="H58" s="10"/>
+      <c r="I58" s="10"/>
+      <c r="J58" s="10"/>
+      <c r="K58" s="10"/>
+      <c r="L58" s="10"/>
+      <c r="M58" s="10"/>
+    </row>
+    <row r="59" customFormat="false" ht="110.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="11" t="s">
         <v>70</v>
       </c>
       <c r="B59" s="11"/>
       <c r="C59" s="11"/>
-    </row>
-    <row r="60" customFormat="false" ht="81.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D59" s="11"/>
+      <c r="E59" s="11"/>
+      <c r="F59" s="11"/>
+      <c r="G59" s="11"/>
+      <c r="H59" s="11"/>
+      <c r="I59" s="11"/>
+      <c r="J59" s="11"/>
+      <c r="K59" s="11"/>
+      <c r="L59" s="11"/>
+      <c r="M59" s="11"/>
+    </row>
+    <row r="60" customFormat="false" ht="61.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="11" t="s">
         <v>71</v>
       </c>
       <c r="B60" s="11"/>
       <c r="C60" s="11"/>
+      <c r="D60" s="11"/>
+      <c r="E60" s="11"/>
+      <c r="F60" s="11"/>
+      <c r="G60" s="11"/>
+      <c r="H60" s="11"/>
+      <c r="I60" s="11"/>
+      <c r="J60" s="11"/>
+      <c r="K60" s="11"/>
+      <c r="L60" s="11"/>
+      <c r="M60" s="11"/>
     </row>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A56:C56"/>
-    <mergeCell ref="A57:C57"/>
-    <mergeCell ref="A58:C58"/>
-    <mergeCell ref="A59:C59"/>
-    <mergeCell ref="A60:C60"/>
+    <mergeCell ref="A56:M56"/>
+    <mergeCell ref="A57:M57"/>
+    <mergeCell ref="A58:M58"/>
+    <mergeCell ref="A59:M59"/>
+    <mergeCell ref="A60:M60"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
